--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-12 08:04</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-13 08:29</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-13 08:29</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-14 09:10</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-14 09:10</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-15 08:52</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-15 08:52</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-16 08:46</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-16 08:46</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-17 08:50</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-17 08:50</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-18 08:25</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-18 08:25</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-19 08:13</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-19 08:13</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-20 08:45</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-20 08:45</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-21 09:12</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-21 09:12</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-22 08:44</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-22 08:44</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-23 08:45</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-23 08:45</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-24 08:39</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-24 08:39</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-25 09:00</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-25 09:00</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-26 08:46</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-26 08:46</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-27 09:27</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-27 09:27</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-28 10:04</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-28 10:04</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-29 10:02</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-29 10:02</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-30 09:55</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-30 09:55</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-01 10:22</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-01 10:22</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-02 09:59</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-02 09:59</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-03 09:21</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-03 09:21</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-04 10:00</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-04 10:00</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-05 10:45</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-05 10:45</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-06 10:38</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-06 10:38</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-07 10:29</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-07 10:29</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-08 10:50</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-08 10:50</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-09 10:49</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-09 10:49</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-10 10:03</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-10 10:03</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-11 10:14</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-11 10:14</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-12 11:12</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-12 11:12</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-13 10:54</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-13 10:54</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-14 08:56</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-14 08:56</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-15 08:30</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-15 08:30</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-16 08:24</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-16 08:24</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-17 07:58</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-17 07:58</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-18 08:14</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-18 08:14</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-19 09:11</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-19 09:11</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-20 08:46</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-20 08:46</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-21 08:47</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-21 08:47</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-22 08:49</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-22 08:49</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-23 08:45</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-23 08:45</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-24 08:20</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-24 08:20</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-25 08:38</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-25 08:38</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-26 09:15</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-26 09:15</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-27 09:15</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-27 09:15</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-28 09:55</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-28 09:55</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-29 10:18</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-29 10:18</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-30 10:20</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-30 10:20</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-10-31 09:53</t>
         </is>
       </c>
     </row>
